--- a/Supplementary_Tables/Supplementary_Table6.xlsx
+++ b/Supplementary_Tables/Supplementary_Table6.xlsx
@@ -1,388 +1,406 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fouladif2/Library/CloudStorage/OneDrive-NationalInstitutesofHealth/Documents/publications/Microbiome_Metabolomics_HIV/Supplementary_Tables/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943D322F-3477-F846-B42D-BC0945BE510C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="17760" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="A.Oral Species" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="B.Oral GO" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="C.Oral SCFA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="A.Oral Species" sheetId="1" r:id="rId1"/>
+    <sheet name="B.Oral GO" sheetId="2" r:id="rId2"/>
+    <sheet name="C.Oral SCFA" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
-  <si>
-    <t xml:space="preserve">Feature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lfc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candidatus Nanosynbacter sp. TM7 075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porphyromonas endodontalis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tannerella serpentiformis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lautropia mirabilis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bohxovirus oralis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aggregatibacter sp. 2125159857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ontology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0015574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trehalose transmembrane transporter activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enables the transfer of trehalose from one side of a membrane to the other. Trehalose is the disaccharide alpha-D-glucopyranosyl-alpha-D-glucopyranoside that acts of a reserve carbohydrate in certain fungi, algae and lichens.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0015771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trehalose transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The directed movement of trehalose into, out of or within a cell, or between cells, by means of some agent such as a transporter or pore. Trehalose is a disaccharide isomeric with sucrose and obtained from certain lichens and fungi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0015942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formate metabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The chemical reactions and pathways involving formate, also known as methanoate, the anion HCOO- derived from methanoic (formic) acid.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:1901681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sulfur compound binding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interacting selectively and non-covalently with a sulfur compound.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0000272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">polysaccharide catabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The chemical reactions and pathways resulting in the breakdown of a polysaccharide, a polymer of many (typically more than 10) monosaccharide residues linked glycosidically.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0035494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNARE complex disassembly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The disaggregation of the SNARE protein complex into its constituent components. The SNARE complex is a protein complex involved in membrane fusion; a stable ternary complex consisting of a four-helix bundle, usually formed from one R-SNARE and three Q-SNAREs with an ionic layer sandwiched between hydrophobic layers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0046537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,3-bisphosphoglycerate-independent phosphoglycerate mutase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalysis of the reaction: 2-phospho-D-glycerate = 3-phospho-D glycerate; this reaction does not require the cofactor 2,3-bisphosphoglycerate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0008663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2',3'-cyclic-nucleotide 2'-phosphodiesterase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalysis of the reaction: nucleoside 2',3'-cyclic phosphate + H2O = nucleoside 3'-phosphate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0015572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-acetylglucosamine transmembrane transporter activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enables the transfer of N-acetylglucosamine from one side of a membrane to the other. The D isomer of N-acetylglucosamine is a common structural unit of glycoproteins in plants, bacteria and animals; it is often the terminal sugar of an oligosaccharide group of a glycoprotein.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0019866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">organelle inner membrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The inner, i.e. lumen-facing, lipid bilayer of an organelle envelope; usually highly selective to most ions and metabolites.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0016485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">protein processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any protein maturation process achieved by the cleavage of a peptide bond or bonds within a protein. Protein maturation is the process leading to the attainment of the full functional capacity of a protein.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0019594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mannitol metabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The chemical reactions and pathways involving mannitol, the alditol derived from D-mannose by reduction of the aldehyde group.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0006047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UDP-N-acetylglucosamine metabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The chemical reactions and pathways involving UDP-N-acetylglucosamine, a substance composed of N-acetylglucosamine, a common structural unit of oligosaccharides, in glycosidic linkage with uridine diphosphate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0030257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type III protein secretion system complex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A complex of approximately 20 proteins, most of which are located in the cytoplasmic membrane that carries out protein secretion in the bacterial type III secretion system; type III secretion also requires a cytoplasmic, probably membrane-associated ATPase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0003910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNA ligase (ATP) activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalysis of the reaction: ATP + deoxyribonucleotide(n) + deoxyribonucleotide(m) = AMP + diphosphate + deoxyribonucleotide(n+m).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0016742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hydroxymethyl-, formyl- and related transferase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalysis of the transfer of a hydroxymethyl- or formyl group from one compound (donor) to another (acceptor).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0031151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">histone methyltransferase activity (H3-K79 specific)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalysis of the reaction: S-adenosyl-L-methionine + histone H3 L-lysine (position 79) = S-adenosyl-L-homocysteine + histone H3 N6-methyl-L-lysine (position 79). This reaction is the addition of a methyl group onto lysine at position 79 of the histone H3 protein.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0009132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nucleoside diphosphate metabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The chemical reactions and pathways involving a nucleoside diphosphate, a compound consisting of a nucleobase linked to a deoxyribose or ribose sugar esterified with diphosphate on the sugar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0009421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bacterial-type flagellum filament cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The proteinaceous structure at the distal tip of the bacterial-type flagellar filament.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0004352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glutamate dehydrogenase (NAD+) activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalysis of the reaction: L-glutamate + H2O + NAD+ = 2-oxoglutarate + NH3 + NADH + H+.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0019551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glutamate catabolic process to 2-oxoglutarate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The chemical reactions and pathways resulting in the breakdown of glutamate into other compounds, including 2-oxoglutarate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0004674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">protein serine/threonine kinase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalysis of the reactions: ATP + protein serine = ADP + protein serine phosphate, and ATP + protein threonine = ADP + protein threonine phosphate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0006397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mRNA processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any process involved in the conversion of a primary mRNA transcript into one or more mature mRNA(s) prior to translation into polypeptide.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0047111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formate dehydrogenase (cytochrome-c-553) activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalysis of the reaction: ferricytochrome C-553 + formate = ferrocytochrome C-553 + CO2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0019062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">virion attachment to host cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The process by which a virion protein binds to molecules on the host cellular surface or host cell surface projection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0070204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-succinyl-5-enolpyruvyl-6-hydroxy-3-cyclohexene-1-carboxylic-acid synthase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalysis of the reaction: 2-oxoglutarate + H(+) + isochorismate = 5-enolpyruvoyl-6-hydroxy-2-succinyl-cyclohex-3-ene-1-carboxylate + CO(2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0030254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">protein secretion by the type III secretion system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The process in which proteins are transferred into the extracellular milieu or directly into host cells by the bacterial type III secretion system; secretion occurs in a continuous process without the distinct presence of periplasmic intermediates and does not involve proteolytic processing of secreted proteins.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0047343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glucose-1-phosphate cytidylyltransferase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalysis of the reaction: alpha-D-glucose 1-phosphate + CTP = CDP-D-glucose + diphosphate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0016539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intein-mediated protein splicing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The removal of an internal amino acid sequence (an intein) from a protein during protein maturation; the excision of inteins is precise and the N- and C-terminal exteins are joined by a normal peptide bond. Protein splicing involves 4 nucleophilic displacements by the 3 conserved splice junction residues.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0030570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pectate lyase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalysis of the reaction: a pectate = a pectate + a pectate oligosaccharide with 4-(4-deoxy-alpha-D-galact-4-enuronosyl)-D-galacturonate end. This reaction is the eliminative cleavage of pectate to give oligosaccharides with 4-deoxy-alpha-D-gluc-4-enuronosyl groups at their non-reducing ends.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0030908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">protein splicing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The post-translational removal of peptide sequences from within a protein sequence.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0008733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-arabinose isomerase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalysis of the reaction: L-arabinose = L-ribulose.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0019299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rhamnose metabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The chemical reactions and pathways involving rhamnose, the hexose 6-deoxy-L-mannose. Rhamnose occurs commonly as a compound of plant glycosides, in polysaccharides of gums and mucilages, and in bacterial polysaccharides. It is also a component of some plant cell wall polysaccharides and frequently acts as the sugar components of flavonoids.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO:0006914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">autophagy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The cellular catabolic process in which cells digest parts of their own cytoplasm; allows for both recycling of macromolecular constituents under conditions of cellular stress and remodeling the intracellular structure for cell differentiation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="121">
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>lfc</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>Candidatus Nanosynbacter sp. TM7 075</t>
+  </si>
+  <si>
+    <t>Porphyromonas endodontalis</t>
+  </si>
+  <si>
+    <t>Tannerella serpentiformis</t>
+  </si>
+  <si>
+    <t>Lautropia mirabilis</t>
+  </si>
+  <si>
+    <t>Bohxovirus oralis</t>
+  </si>
+  <si>
+    <t>Aggregatibacter sp. 2125159857</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Ontology</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>GO:0015574</t>
+  </si>
+  <si>
+    <t>trehalose transmembrane transporter activity</t>
+  </si>
+  <si>
+    <t>MF</t>
+  </si>
+  <si>
+    <t>Enables the transfer of trehalose from one side of a membrane to the other. Trehalose is the disaccharide alpha-D-glucopyranosyl-alpha-D-glucopyranoside that acts of a reserve carbohydrate in certain fungi, algae and lichens.</t>
+  </si>
+  <si>
+    <t>GO:0015771</t>
+  </si>
+  <si>
+    <t>trehalose transport</t>
+  </si>
+  <si>
+    <t>BP</t>
+  </si>
+  <si>
+    <t>The directed movement of trehalose into, out of or within a cell, or between cells, by means of some agent such as a transporter or pore. Trehalose is a disaccharide isomeric with sucrose and obtained from certain lichens and fungi.</t>
+  </si>
+  <si>
+    <t>GO:0015942</t>
+  </si>
+  <si>
+    <t>formate metabolic process</t>
+  </si>
+  <si>
+    <t>The chemical reactions and pathways involving formate, also known as methanoate, the anion HCOO- derived from methanoic (formic) acid.</t>
+  </si>
+  <si>
+    <t>GO:1901681</t>
+  </si>
+  <si>
+    <t>sulfur compound binding</t>
+  </si>
+  <si>
+    <t>Interacting selectively and non-covalently with a sulfur compound.</t>
+  </si>
+  <si>
+    <t>GO:0000272</t>
+  </si>
+  <si>
+    <t>polysaccharide catabolic process</t>
+  </si>
+  <si>
+    <t>The chemical reactions and pathways resulting in the breakdown of a polysaccharide, a polymer of many (typically more than 10) monosaccharide residues linked glycosidically.</t>
+  </si>
+  <si>
+    <t>GO:0035494</t>
+  </si>
+  <si>
+    <t>SNARE complex disassembly</t>
+  </si>
+  <si>
+    <t>The disaggregation of the SNARE protein complex into its constituent components. The SNARE complex is a protein complex involved in membrane fusion; a stable ternary complex consisting of a four-helix bundle, usually formed from one R-SNARE and three Q-SNAREs with an ionic layer sandwiched between hydrophobic layers.</t>
+  </si>
+  <si>
+    <t>GO:0046537</t>
+  </si>
+  <si>
+    <t>2,3-bisphosphoglycerate-independent phosphoglycerate mutase activity</t>
+  </si>
+  <si>
+    <t>Catalysis of the reaction: 2-phospho-D-glycerate = 3-phospho-D glycerate; this reaction does not require the cofactor 2,3-bisphosphoglycerate.</t>
+  </si>
+  <si>
+    <t>GO:0008663</t>
+  </si>
+  <si>
+    <t>2',3'-cyclic-nucleotide 2'-phosphodiesterase activity</t>
+  </si>
+  <si>
+    <t>Catalysis of the reaction: nucleoside 2',3'-cyclic phosphate + H2O = nucleoside 3'-phosphate.</t>
+  </si>
+  <si>
+    <t>GO:0015572</t>
+  </si>
+  <si>
+    <t>N-acetylglucosamine transmembrane transporter activity</t>
+  </si>
+  <si>
+    <t>Enables the transfer of N-acetylglucosamine from one side of a membrane to the other. The D isomer of N-acetylglucosamine is a common structural unit of glycoproteins in plants, bacteria and animals; it is often the terminal sugar of an oligosaccharide group of a glycoprotein.</t>
+  </si>
+  <si>
+    <t>GO:0019866</t>
+  </si>
+  <si>
+    <t>organelle inner membrane</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>The inner, i.e. lumen-facing, lipid bilayer of an organelle envelope; usually highly selective to most ions and metabolites.</t>
+  </si>
+  <si>
+    <t>GO:0016485</t>
+  </si>
+  <si>
+    <t>protein processing</t>
+  </si>
+  <si>
+    <t>Any protein maturation process achieved by the cleavage of a peptide bond or bonds within a protein. Protein maturation is the process leading to the attainment of the full functional capacity of a protein.</t>
+  </si>
+  <si>
+    <t>GO:0019594</t>
+  </si>
+  <si>
+    <t>mannitol metabolic process</t>
+  </si>
+  <si>
+    <t>The chemical reactions and pathways involving mannitol, the alditol derived from D-mannose by reduction of the aldehyde group.</t>
+  </si>
+  <si>
+    <t>GO:0006047</t>
+  </si>
+  <si>
+    <t>UDP-N-acetylglucosamine metabolic process</t>
+  </si>
+  <si>
+    <t>The chemical reactions and pathways involving UDP-N-acetylglucosamine, a substance composed of N-acetylglucosamine, a common structural unit of oligosaccharides, in glycosidic linkage with uridine diphosphate.</t>
+  </si>
+  <si>
+    <t>GO:0030257</t>
+  </si>
+  <si>
+    <t>type III protein secretion system complex</t>
+  </si>
+  <si>
+    <t>A complex of approximately 20 proteins, most of which are located in the cytoplasmic membrane that carries out protein secretion in the bacterial type III secretion system; type III secretion also requires a cytoplasmic, probably membrane-associated ATPase.</t>
+  </si>
+  <si>
+    <t>GO:0003910</t>
+  </si>
+  <si>
+    <t>DNA ligase (ATP) activity</t>
+  </si>
+  <si>
+    <t>Catalysis of the reaction: ATP + deoxyribonucleotide(n) + deoxyribonucleotide(m) = AMP + diphosphate + deoxyribonucleotide(n+m).</t>
+  </si>
+  <si>
+    <t>GO:0016742</t>
+  </si>
+  <si>
+    <t>hydroxymethyl-, formyl- and related transferase activity</t>
+  </si>
+  <si>
+    <t>Catalysis of the transfer of a hydroxymethyl- or formyl group from one compound (donor) to another (acceptor).</t>
+  </si>
+  <si>
+    <t>GO:0031151</t>
+  </si>
+  <si>
+    <t>histone methyltransferase activity (H3-K79 specific)</t>
+  </si>
+  <si>
+    <t>Catalysis of the reaction: S-adenosyl-L-methionine + histone H3 L-lysine (position 79) = S-adenosyl-L-homocysteine + histone H3 N6-methyl-L-lysine (position 79). This reaction is the addition of a methyl group onto lysine at position 79 of the histone H3 protein.</t>
+  </si>
+  <si>
+    <t>GO:0009132</t>
+  </si>
+  <si>
+    <t>nucleoside diphosphate metabolic process</t>
+  </si>
+  <si>
+    <t>The chemical reactions and pathways involving a nucleoside diphosphate, a compound consisting of a nucleobase linked to a deoxyribose or ribose sugar esterified with diphosphate on the sugar.</t>
+  </si>
+  <si>
+    <t>GO:0009421</t>
+  </si>
+  <si>
+    <t>bacterial-type flagellum filament cap</t>
+  </si>
+  <si>
+    <t>The proteinaceous structure at the distal tip of the bacterial-type flagellar filament.</t>
+  </si>
+  <si>
+    <t>GO:0004352</t>
+  </si>
+  <si>
+    <t>glutamate dehydrogenase (NAD+) activity</t>
+  </si>
+  <si>
+    <t>Catalysis of the reaction: L-glutamate + H2O + NAD+ = 2-oxoglutarate + NH3 + NADH + H+.</t>
+  </si>
+  <si>
+    <t>GO:0019551</t>
+  </si>
+  <si>
+    <t>glutamate catabolic process to 2-oxoglutarate</t>
+  </si>
+  <si>
+    <t>The chemical reactions and pathways resulting in the breakdown of glutamate into other compounds, including 2-oxoglutarate.</t>
+  </si>
+  <si>
+    <t>GO:0004674</t>
+  </si>
+  <si>
+    <t>protein serine/threonine kinase activity</t>
+  </si>
+  <si>
+    <t>Catalysis of the reactions: ATP + protein serine = ADP + protein serine phosphate, and ATP + protein threonine = ADP + protein threonine phosphate.</t>
+  </si>
+  <si>
+    <t>GO:0006397</t>
+  </si>
+  <si>
+    <t>mRNA processing</t>
+  </si>
+  <si>
+    <t>Any process involved in the conversion of a primary mRNA transcript into one or more mature mRNA(s) prior to translation into polypeptide.</t>
+  </si>
+  <si>
+    <t>GO:0047111</t>
+  </si>
+  <si>
+    <t>formate dehydrogenase (cytochrome-c-553) activity</t>
+  </si>
+  <si>
+    <t>Catalysis of the reaction: ferricytochrome C-553 + formate = ferrocytochrome C-553 + CO2.</t>
+  </si>
+  <si>
+    <t>GO:0019062</t>
+  </si>
+  <si>
+    <t>virion attachment to host cell</t>
+  </si>
+  <si>
+    <t>The process by which a virion protein binds to molecules on the host cellular surface or host cell surface projection.</t>
+  </si>
+  <si>
+    <t>GO:0070204</t>
+  </si>
+  <si>
+    <t>2-succinyl-5-enolpyruvyl-6-hydroxy-3-cyclohexene-1-carboxylic-acid synthase activity</t>
+  </si>
+  <si>
+    <t>Catalysis of the reaction: 2-oxoglutarate + H(+) + isochorismate = 5-enolpyruvoyl-6-hydroxy-2-succinyl-cyclohex-3-ene-1-carboxylate + CO(2).</t>
+  </si>
+  <si>
+    <t>GO:0030254</t>
+  </si>
+  <si>
+    <t>protein secretion by the type III secretion system</t>
+  </si>
+  <si>
+    <t>The process in which proteins are transferred into the extracellular milieu or directly into host cells by the bacterial type III secretion system; secretion occurs in a continuous process without the distinct presence of periplasmic intermediates and does not involve proteolytic processing of secreted proteins.</t>
+  </si>
+  <si>
+    <t>GO:0047343</t>
+  </si>
+  <si>
+    <t>glucose-1-phosphate cytidylyltransferase activity</t>
+  </si>
+  <si>
+    <t>Catalysis of the reaction: alpha-D-glucose 1-phosphate + CTP = CDP-D-glucose + diphosphate.</t>
+  </si>
+  <si>
+    <t>GO:0016539</t>
+  </si>
+  <si>
+    <t>intein-mediated protein splicing</t>
+  </si>
+  <si>
+    <t>The removal of an internal amino acid sequence (an intein) from a protein during protein maturation; the excision of inteins is precise and the N- and C-terminal exteins are joined by a normal peptide bond. Protein splicing involves 4 nucleophilic displacements by the 3 conserved splice junction residues.</t>
+  </si>
+  <si>
+    <t>GO:0030570</t>
+  </si>
+  <si>
+    <t>pectate lyase activity</t>
+  </si>
+  <si>
+    <t>Catalysis of the reaction: a pectate = a pectate + a pectate oligosaccharide with 4-(4-deoxy-alpha-D-galact-4-enuronosyl)-D-galacturonate end. This reaction is the eliminative cleavage of pectate to give oligosaccharides with 4-deoxy-alpha-D-gluc-4-enuronosyl groups at their non-reducing ends.</t>
+  </si>
+  <si>
+    <t>GO:0030908</t>
+  </si>
+  <si>
+    <t>protein splicing</t>
+  </si>
+  <si>
+    <t>The post-translational removal of peptide sequences from within a protein sequence.</t>
+  </si>
+  <si>
+    <t>GO:0008733</t>
+  </si>
+  <si>
+    <t>L-arabinose isomerase activity</t>
+  </si>
+  <si>
+    <t>Catalysis of the reaction: L-arabinose = L-ribulose.</t>
+  </si>
+  <si>
+    <t>GO:0019299</t>
+  </si>
+  <si>
+    <t>rhamnose metabolic process</t>
+  </si>
+  <si>
+    <t>The chemical reactions and pathways involving rhamnose, the hexose 6-deoxy-L-mannose. Rhamnose occurs commonly as a compound of plant glycosides, in polysaccharides of gums and mucilages, and in bacterial polysaccharides. It is also a component of some plant cell wall polysaccharides and frequently acts as the sugar components of flavonoids.</t>
+  </si>
+  <si>
+    <t>GO:0006914</t>
+  </si>
+  <si>
+    <t>autophagy</t>
+  </si>
+  <si>
+    <t>The cellular catabolic process in which cells digest parts of their own cytoplasm; allows for both recycling of macromolecular constituents under conditions of cellular stress and remodeling the intracellular structure for cell differentiation.</t>
+  </si>
+  <si>
+    <t>SCFA</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>Supplementary Table 6 (Differential abundance analysis of oral microbiome and oral short chain fatty acids between Pre-HIV and Non-HIV).  A-B. Differential abundance analysis (DAA) between Pre-HIV and Non-HIV. A-B. Log-fold changes (LFC) of absolute abundances are presented for differentially abundant features (p&lt;0.01). Positive LFC represents a higher abundance in Pre-HIV and negative LFC represents a lower abundance in Pre-HIV compared to Non-HIV. q-values are adjusted p-values for multiple hypothesis testing using the Benjamini-Hochberg procedure. These results are obtained by applying ANCOM-BC2. A. DAA of oral bacterial species. B. DAA of oral microbial Gene Ontology (GO) terms. C. Oral short chain fatty acids (SCFA). The significance of results for oral (SCFA) is based on linear regression analysis. The sample sizes vary by data modality as described in Supplementary Table 12.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -410,13 +428,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -698,120 +728,135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.00188320070578334</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.124477720942537</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
+      <c r="B3">
+        <v>0.79400000000000004</v>
+      </c>
+      <c r="C3">
+        <v>1.88320070578334E-3</v>
+      </c>
+      <c r="D3">
+        <v>0.12447772094253701</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B4">
         <v>1.163</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.001192708399488</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.124477720942537</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
+      <c r="C4">
+        <v>1.192708399488E-3</v>
+      </c>
+      <c r="D4">
+        <v>0.12447772094253701</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B5">
         <v>-0.82</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.00396942582501665</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C5">
+        <v>3.96942582501665E-3</v>
+      </c>
+      <c r="D5">
         <v>0.152822894263141</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="n">
-        <v>-1.156</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.00922280480235284</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.202901705651762</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
+      <c r="B6">
+        <v>-1.1559999999999999</v>
+      </c>
+      <c r="C6">
+        <v>9.2228048023528398E-3</v>
+      </c>
+      <c r="D6">
+        <v>0.20290170565176199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.784</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.00883902186010983</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.202901705651762</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
+      <c r="B7">
+        <v>0.78400000000000003</v>
+      </c>
+      <c r="C7">
+        <v>8.8390218601098296E-3</v>
+      </c>
+      <c r="D7">
+        <v>0.20290170565176199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B8">
         <v>0.873</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.00894511262935781</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.202901705651762</v>
+      <c r="C8">
+        <v>8.9451126293578105E-3</v>
+      </c>
+      <c r="D8">
+        <v>0.20290170565176199</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -834,21 +879,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>-0.4</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.00110656177898718</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0769265355244048</v>
+      <c r="D2">
+        <v>1.1065617789871799E-3</v>
+      </c>
+      <c r="E2">
+        <v>7.6926535524404802E-2</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
@@ -857,21 +902,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>-0.4</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.00110656177898718</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.0769265355244048</v>
+      <c r="D3">
+        <v>1.1065617789871799E-3</v>
+      </c>
+      <c r="E3">
+        <v>7.6926535524404802E-2</v>
       </c>
       <c r="F3" t="s">
         <v>19</v>
@@ -880,21 +925,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0.37</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.00114799424863158</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0769566144529099</v>
+      <c r="D4">
+        <v>1.14799424863158E-3</v>
+      </c>
+      <c r="E4">
+        <v>7.6956614452909897E-2</v>
       </c>
       <c r="F4" t="s">
         <v>19</v>
@@ -903,21 +948,21 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>24</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="n">
-        <v>-0.396</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.00153553610303429</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.0993862505308748</v>
+      <c r="C5">
+        <v>-0.39600000000000002</v>
+      </c>
+      <c r="D5">
+        <v>1.53553610303429E-3</v>
+      </c>
+      <c r="E5">
+        <v>9.9386250530874798E-2</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
@@ -926,20 +971,20 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="n">
-        <v>-0.464</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.00174145450027475</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="C6">
+        <v>-0.46400000000000002</v>
+      </c>
+      <c r="D6">
+        <v>1.7414545002747499E-3</v>
+      </c>
+      <c r="E6">
         <v>0.105442261194055</v>
       </c>
       <c r="F6" t="s">
@@ -949,20 +994,20 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>-0.255</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.00169118265920879</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7">
+        <v>1.69118265920879E-3</v>
+      </c>
+      <c r="E7">
         <v>0.105442261194055</v>
       </c>
       <c r="F7" t="s">
@@ -972,20 +1017,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>33</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="n">
-        <v>-0.513</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.00193765333998584</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="C8">
+        <v>-0.51300000000000001</v>
+      </c>
+      <c r="D8">
+        <v>1.9376533399858399E-3</v>
+      </c>
+      <c r="E8">
         <v>0.110925308680763</v>
       </c>
       <c r="F8" t="s">
@@ -995,20 +1040,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>36</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.00195020521388662</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="C9">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="D9">
+        <v>1.95020521388662E-3</v>
+      </c>
+      <c r="E9">
         <v>0.110925308680763</v>
       </c>
       <c r="F9" t="s">
@@ -1018,21 +1063,21 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
       <c r="B10" t="s">
         <v>40</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.00227763911885422</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.125739077237923</v>
+      <c r="C10">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="D10">
+        <v>2.27763911885422E-3</v>
+      </c>
+      <c r="E10">
+        <v>0.12573907723792299</v>
       </c>
       <c r="F10" t="s">
         <v>15</v>
@@ -1041,21 +1086,21 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>42</v>
       </c>
       <c r="B11" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.00247161184930647</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.132549012604236</v>
+      <c r="C11">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="D11">
+        <v>2.4716118493064701E-3</v>
+      </c>
+      <c r="E11">
+        <v>0.13254901260423599</v>
       </c>
       <c r="F11" t="s">
         <v>44</v>
@@ -1064,21 +1109,21 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>46</v>
       </c>
       <c r="B12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.00270025689013519</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.140788393966215</v>
+      <c r="C12">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="D12">
+        <v>2.7002568901351898E-3</v>
+      </c>
+      <c r="E12">
+        <v>0.14078839396621501</v>
       </c>
       <c r="F12" t="s">
         <v>19</v>
@@ -1087,20 +1132,20 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>49</v>
       </c>
       <c r="B13" t="s">
         <v>50</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>0.4</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.00291644406176643</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="D13">
+        <v>2.9164440617664299E-3</v>
+      </c>
+      <c r="E13">
         <v>0.147950419025286</v>
       </c>
       <c r="F13" t="s">
@@ -1110,21 +1155,21 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>52</v>
       </c>
       <c r="B14" t="s">
         <v>53</v>
       </c>
-      <c r="C14" t="n">
-        <v>-0.243</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.00366814635785423</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.17212776784231</v>
+      <c r="C14">
+        <v>-0.24299999999999999</v>
+      </c>
+      <c r="D14">
+        <v>3.6681463578542299E-3</v>
+      </c>
+      <c r="E14">
+        <v>0.17212776784230999</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
@@ -1133,21 +1178,21 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>55</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
       </c>
-      <c r="C15" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.00349298633370936</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.17212776784231</v>
+      <c r="C15">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="D15">
+        <v>3.4929863337093601E-3</v>
+      </c>
+      <c r="E15">
+        <v>0.17212776784230999</v>
       </c>
       <c r="F15" t="s">
         <v>44</v>
@@ -1156,21 +1201,21 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>58</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
       </c>
-      <c r="C16" t="n">
-        <v>0.565</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.00361112837541713</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.17212776784231</v>
+      <c r="C16">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D16">
+        <v>3.61112837541713E-3</v>
+      </c>
+      <c r="E16">
+        <v>0.17212776784230999</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
@@ -1179,21 +1224,21 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>61</v>
       </c>
       <c r="B17" t="s">
         <v>62</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>0.31</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.00419197117230042</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.1919104851319</v>
+      <c r="D17">
+        <v>4.1919711723004197E-3</v>
+      </c>
+      <c r="E17">
+        <v>0.19191048513190001</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
@@ -1202,20 +1247,20 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>64</v>
       </c>
       <c r="B18" t="s">
         <v>65</v>
       </c>
-      <c r="C18" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.00482615443303995</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="C18">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="D18">
+        <v>4.8261544330399503E-3</v>
+      </c>
+      <c r="E18">
         <v>0.205879360700364</v>
       </c>
       <c r="F18" t="s">
@@ -1225,20 +1270,20 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>67</v>
       </c>
       <c r="B19" t="s">
         <v>68</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>0.309</v>
       </c>
-      <c r="D19" t="n">
-        <v>0.00478255183396605</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="D19">
+        <v>4.7825518339660502E-3</v>
+      </c>
+      <c r="E19">
         <v>0.205879360700364</v>
       </c>
       <c r="F19" t="s">
@@ -1248,20 +1293,20 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>70</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
       </c>
-      <c r="C20" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.00464354156079896</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="C20">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="D20">
+        <v>4.6435415607989604E-3</v>
+      </c>
+      <c r="E20">
         <v>0.205879360700364</v>
       </c>
       <c r="F20" t="s">
@@ -1271,21 +1316,21 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>73</v>
       </c>
       <c r="B21" t="s">
         <v>74</v>
       </c>
-      <c r="C21" t="n">
-        <v>-0.636</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.00669130361299367</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.243919457486769</v>
+      <c r="C21">
+        <v>-0.63600000000000001</v>
+      </c>
+      <c r="D21">
+        <v>6.6913036129936697E-3</v>
+      </c>
+      <c r="E21">
+        <v>0.24391945748676899</v>
       </c>
       <c r="F21" t="s">
         <v>15</v>
@@ -1294,21 +1339,21 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>76</v>
       </c>
       <c r="B22" t="s">
         <v>77</v>
       </c>
-      <c r="C22" t="n">
-        <v>-0.636</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.00669130361299367</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.243919457486769</v>
+      <c r="C22">
+        <v>-0.63600000000000001</v>
+      </c>
+      <c r="D22">
+        <v>6.6913036129936697E-3</v>
+      </c>
+      <c r="E22">
+        <v>0.24391945748676899</v>
       </c>
       <c r="F22" t="s">
         <v>19</v>
@@ -1317,21 +1362,21 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>79</v>
       </c>
       <c r="B23" t="s">
         <v>80</v>
       </c>
-      <c r="C23" t="n">
-        <v>-0.367</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.00695500005532646</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.243919457486769</v>
+      <c r="C23">
+        <v>-0.36699999999999999</v>
+      </c>
+      <c r="D23">
+        <v>6.9550000553264598E-3</v>
+      </c>
+      <c r="E23">
+        <v>0.24391945748676899</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
@@ -1340,21 +1385,21 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>82</v>
       </c>
       <c r="B24" t="s">
         <v>83</v>
       </c>
-      <c r="C24" t="n">
-        <v>-0.332</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.00597639192966327</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.243919457486769</v>
+      <c r="C24">
+        <v>-0.33200000000000002</v>
+      </c>
+      <c r="D24">
+        <v>5.9763919296632701E-3</v>
+      </c>
+      <c r="E24">
+        <v>0.24391945748676899</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -1363,21 +1408,21 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>85</v>
       </c>
       <c r="B25" t="s">
         <v>86</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.00673372713969304</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.243919457486769</v>
+      <c r="C25">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="D25">
+        <v>6.7337271396930402E-3</v>
+      </c>
+      <c r="E25">
+        <v>0.24391945748676899</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
@@ -1386,21 +1431,21 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>88</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
       </c>
-      <c r="C26" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.00671390826420503</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.243919457486769</v>
+      <c r="C26">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="D26">
+        <v>6.7139082642050296E-3</v>
+      </c>
+      <c r="E26">
+        <v>0.24391945748676899</v>
       </c>
       <c r="F26" t="s">
         <v>19</v>
@@ -1409,21 +1454,21 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>91</v>
       </c>
       <c r="B27" t="s">
         <v>92</v>
       </c>
-      <c r="C27" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.00701739515412121</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.243919457486769</v>
+      <c r="C27">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="D27">
+        <v>7.0173951541212098E-3</v>
+      </c>
+      <c r="E27">
+        <v>0.24391945748676899</v>
       </c>
       <c r="F27" t="s">
         <v>15</v>
@@ -1432,21 +1477,21 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>94</v>
       </c>
       <c r="B28" t="s">
         <v>95</v>
       </c>
-      <c r="C28" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.00597916651440885</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.243919457486769</v>
+      <c r="C28">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="D28">
+        <v>5.9791665144088499E-3</v>
+      </c>
+      <c r="E28">
+        <v>0.24391945748676899</v>
       </c>
       <c r="F28" t="s">
         <v>19</v>
@@ -1455,21 +1500,21 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>97</v>
       </c>
       <c r="B29" t="s">
         <v>98</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>0.4</v>
       </c>
-      <c r="D29" t="n">
-        <v>0.00672826540627663</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.243919457486769</v>
+      <c r="D29">
+        <v>6.7282654062766302E-3</v>
+      </c>
+      <c r="E29">
+        <v>0.24391945748676899</v>
       </c>
       <c r="F29" t="s">
         <v>15</v>
@@ -1478,21 +1523,21 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>100</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
       </c>
-      <c r="C30" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.00686053034294352</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.243919457486769</v>
+      <c r="C30">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="D30">
+        <v>6.86053034294352E-3</v>
+      </c>
+      <c r="E30">
+        <v>0.24391945748676899</v>
       </c>
       <c r="F30" t="s">
         <v>19</v>
@@ -1501,20 +1546,20 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>103</v>
       </c>
       <c r="B31" t="s">
         <v>104</v>
       </c>
-      <c r="C31" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.00718012319284591</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="C31">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="D31">
+        <v>7.1801231928459103E-3</v>
+      </c>
+      <c r="E31">
         <v>0.245038022417669</v>
       </c>
       <c r="F31" t="s">
@@ -1524,21 +1569,21 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>106</v>
       </c>
       <c r="B32" t="s">
         <v>107</v>
       </c>
-      <c r="C32" t="n">
-        <v>-0.306</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.00743520178040065</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.245715452570253</v>
+      <c r="C32">
+        <v>-0.30599999999999999</v>
+      </c>
+      <c r="D32">
+        <v>7.4352017804006501E-3</v>
+      </c>
+      <c r="E32">
+        <v>0.24571545257025301</v>
       </c>
       <c r="F32" t="s">
         <v>19</v>
@@ -1547,21 +1592,21 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>109</v>
       </c>
       <c r="B33" t="s">
         <v>110</v>
       </c>
-      <c r="C33" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.00746179051491976</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.245715452570253</v>
+      <c r="C33">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="D33">
+        <v>7.4617905149197599E-3</v>
+      </c>
+      <c r="E33">
+        <v>0.24571545257025301</v>
       </c>
       <c r="F33" t="s">
         <v>15</v>
@@ -1570,21 +1615,21 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>112</v>
       </c>
       <c r="B34" t="s">
         <v>113</v>
       </c>
-      <c r="C34" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.00887116125359562</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.287089132293086</v>
+      <c r="C34">
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="D34">
+        <v>8.8711612535956191E-3</v>
+      </c>
+      <c r="E34">
+        <v>0.28708913229308602</v>
       </c>
       <c r="F34" t="s">
         <v>19</v>
@@ -1593,20 +1638,20 @@
         <v>114</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>115</v>
       </c>
       <c r="B35" t="s">
         <v>116</v>
       </c>
-      <c r="C35" t="n">
-        <v>-0.256</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.00940165558760479</v>
-      </c>
-      <c r="E35" t="n">
+      <c r="C35">
+        <v>-0.25600000000000001</v>
+      </c>
+      <c r="D35">
+        <v>9.4016555876047896E-3</v>
+      </c>
+      <c r="E35">
         <v>0.299100127761596</v>
       </c>
       <c r="F35" t="s">
@@ -1618,16 +1663,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>118</v>
       </c>
@@ -1640,6 +1685,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>